--- a/travel_agent_forms/007_travel_planning_questionnaire--travel_agent_forms.xlsx
+++ b/travel_agent_forms/007_travel_planning_questionnaire--travel_agent_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,12 +437,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E15"/>
+  <dimension ref="A1:E13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="19" customWidth="1" min="2" max="2"/>
-    <col width="19" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="50" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -515,138 +515,138 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>travel_agent_form</t>
+          <t>travel_date</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Travel Agent Form</t>
+          <t>What is the travel date?</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>travel_date</t>
+          <t>travel_length</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>travel_date</t>
+          <t>How long do you plan to travel?</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>travel_length</t>
+          <t>travel_agent</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>travel_length</t>
+          <t>Who is your preferred travel agent?</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>travel_agent</t>
+          <t>travel_agents</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>travel_agent</t>
+          <t>Which travel agents do you prefer to contact for your travel plans?</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>travel_agent_form</t>
+          <t>travel_budget</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Travel Agent Form</t>
+          <t>What is your travel budget?</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>time</t>
+          <t>note</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>travel_duration</t>
+          <t>travel_notes</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>travel_duration</t>
+          <t>Do you have any travel notes or comments?</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -658,64 +658,64 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>travel_budget</t>
+          <t>travel_email</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>travel_budget</t>
+          <t>What is your email address?</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>travel_notes</t>
+          <t>travel_phone</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>travel_notes</t>
+          <t>What is your phone number?</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>travel_email</t>
+          <t>travel_days</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>travel_email</t>
+          <t>How many days do you plan to stay?</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -727,62 +727,16 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>travel_phone</t>
+          <t>travel_form</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>travel_phone</t>
+          <t>Do you have any other requests or questions for us?</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>travel_agent_form</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Travel Agent Form</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr"/>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>travel_length</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>travel_length</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr"/>
-      <c r="E15" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -802,9 +756,9 @@
   <dimension ref="A1:C10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="27" customWidth="1" min="1" max="1"/>
-    <col width="24" customWidth="1" min="2" max="2"/>
-    <col width="24" customWidth="1" min="3" max="3"/>
+    <col width="23" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -832,12 +786,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'text':_'agent_a'}</t>
+          <t>one_day</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'text': 'Agent A'}</t>
+          <t>One day</t>
         </is>
       </c>
     </row>
@@ -849,12 +803,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'text':_'agent_b'}</t>
+          <t>two_days</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'text': 'Agent B'}</t>
+          <t>Two days</t>
         </is>
       </c>
     </row>
@@ -866,114 +820,114 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'text':_'agent_c'}</t>
+          <t>three_days</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'text': 'Agent C'}</t>
+          <t>Three days</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>travel_agent_form_choices</t>
+          <t>travel_agents_choices</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'text':_'agent_a'}</t>
+          <t>agent_a</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'text': 'Agent A'}</t>
+          <t>Agent A</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>travel_agent_form_choices</t>
+          <t>travel_agents_choices</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'text':_'agent_b'}</t>
+          <t>agent_b</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'text': 'Agent B'}</t>
+          <t>Agent B</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>travel_agent_form_choices</t>
+          <t>travel_agents_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'text':_'agent_c'}</t>
+          <t>agent_c</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'text': 'Agent C'}</t>
+          <t>Agent C</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>travel_length_choices</t>
+          <t>travel_days_choices</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'text':_'one_day'}</t>
+          <t>one_day</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'text': 'One day'}</t>
+          <t>One day</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>travel_length_choices</t>
+          <t>travel_days_choices</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'text':_'two_days'}</t>
+          <t>two_days</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'text': 'Two days'}</t>
+          <t>Two days</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>travel_length_choices</t>
+          <t>travel_days_choices</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'text':_'three_days'}</t>
+          <t>three_days</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'text': 'Three days'}</t>
+          <t>Three days</t>
         </is>
       </c>
     </row>
